--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User2\Documents\UiPath\TaxReturnReceivedReport_Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F383A325-8856-443F-A4BC-2164B87000F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8099AD-514B-4CE9-A63C-50F1CCE50C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>C:\Users\ALTFEST_DA_User2\Documents\Altfest\Output\2025 Tax Returns Received 06.30.26.xlsx</t>
+  </si>
+  <si>
+    <t>FullNamePositionMasterFile</t>
+  </si>
+  <si>
+    <t>MatchTablesPrompt</t>
   </si>
 </sst>
 </file>
@@ -2046,22 +2052,29 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -3125,7 +3138,17 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User2\Documents\UiPath\TaxReturnReceivedReport_Process\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User1\Documents\UiPath\Altfest_TaxReturnP1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8099AD-514B-4CE9-A63C-50F1CCE50C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82211B26-19B5-4F75-8676-33179EC555FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
   <si>
     <t>Name</t>
   </si>
@@ -201,9 +201,6 @@
     <t>Sheet1</t>
   </si>
   <si>
-    <t>C:\Users\ALTFEST_DA_User2\Documents\TaxReturn_Template.xlsx</t>
-  </si>
-  <si>
     <t>MasterFilePath</t>
   </si>
   <si>
@@ -282,13 +279,22 @@
     <t>Altfest_CurrentFileDate</t>
   </si>
   <si>
-    <t>C:\Users\ALTFEST_DA_User2\Documents\Altfest\Output\2025 Tax Returns Received 06.30.26.xlsx</t>
-  </si>
-  <si>
     <t>FullNamePositionMasterFile</t>
   </si>
   <si>
     <t>MatchTablesPrompt</t>
+  </si>
+  <si>
+    <t>C:\Users\ALTFEST_DA_User1\Downloads\2026 CLIENT ENGAGEMENT TRACKER.xlsx</t>
+  </si>
+  <si>
+    <t>MasterFilePath1</t>
+  </si>
+  <si>
+    <t>C:\Users\ALTFEST_DA_User1\Documents\TaxReturnPt1\Output\2025 Tax Returns Received 07.31.26.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\ALTFEST_DA_User1\Documents\TaxReturnPt1\TaxReturnOutput_Template.xlsx</t>
   </si>
 </sst>
 </file>
@@ -330,12 +336,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -350,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -364,6 +376,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1757,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z987"/>
+  <dimension ref="A1:Z988"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1953,7 +1969,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -1964,12 +1980,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:3" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
-        <v>54</v>
+      <c r="B22" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -1980,87 +1996,94 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
+    <row r="24" spans="1:3" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
+    <row r="25" spans="1:3" s="10" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
+        <v>61</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" t="s">
-        <v>77</v>
+      <c r="A30" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>79</v>
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>81</v>
+      <c r="B34">
+        <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
@@ -3014,6 +3037,7 @@
     <row r="985" ht="14.25" customHeight="1"/>
     <row r="986" ht="14.25" customHeight="1"/>
     <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3070,80 +3094,80 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User1\Documents\UiPath\Altfest_TaxReturnP1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82211B26-19B5-4F75-8676-33179EC555FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF88CB8-9200-4C69-9D66-31EDCC16C6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,9 +243,6 @@
     <t>Stores the login URL used to access Practifi for Altfest.</t>
   </si>
   <si>
-    <t>C:\Users\ALTFEST_DA_User2\Documents\Altfest\Output\[PreviousYear] Tax Returns Received [CurrentDate].xlsx</t>
-  </si>
-  <si>
     <t>MaxApiRetry</t>
   </si>
   <si>
@@ -291,10 +288,13 @@
     <t>MasterFilePath1</t>
   </si>
   <si>
-    <t>C:\Users\ALTFEST_DA_User1\Documents\TaxReturnPt1\Output\2025 Tax Returns Received 07.31.26.xlsx</t>
-  </si>
-  <si>
-    <t>C:\Users\ALTFEST_DA_User1\Documents\TaxReturnPt1\TaxReturnOutput_Template.xlsx</t>
+    <t>[DocumentFolderPath]\TaxReturnPt1\TaxReturnOutput_Template.xlsx</t>
+  </si>
+  <si>
+    <t>[DocumentFolderPath]\TaxReturnPt1\Output\2025 Tax Returns Received 07.31.26.xlsx</t>
+  </si>
+  <si>
+    <t>[DocumentFolderPath]\TaxReturnPt1\Output\[PreviousYear] Tax Returns Received [CurrentDate].xlsx</t>
   </si>
 </sst>
 </file>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -378,8 +378,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1964,12 +1962,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:3" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B20" t="s">
-        <v>68</v>
+      <c r="B20" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -1985,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -2001,15 +1999,15 @@
         <v>54</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" s="10" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>70</v>
+      <c r="B25" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
@@ -2038,7 +2036,7 @@
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -2046,31 +2044,31 @@
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
         <v>76</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:2" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>84</v>
@@ -2078,7 +2076,7 @@
     </row>
     <row r="34" spans="1:2" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -3117,7 +3115,7 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -3131,7 +3129,7 @@
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -3145,7 +3143,7 @@
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
@@ -3164,10 +3162,10 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User1\Documents\UiPath\Altfest_TaxReturnP1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF88CB8-9200-4C69-9D66-31EDCC16C6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C6E5F-8C2B-484A-AA81-EFC6572873FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="85">
   <si>
     <t>Name</t>
   </si>
@@ -201,100 +201,97 @@
     <t>Sheet1</t>
   </si>
   <si>
+    <t>MasterFileSheet</t>
+  </si>
+  <si>
+    <t>MAIN SHEET</t>
+  </si>
+  <si>
+    <t>SubjectFinalEmail</t>
+  </si>
+  <si>
+    <t>[PreviousYear] Tax Returns Received</t>
+  </si>
+  <si>
+    <t>Altfest_CustomerMail</t>
+  </si>
+  <si>
+    <t>Altfest_SupportMail</t>
+  </si>
+  <si>
+    <t>BodyFinalEmail</t>
+  </si>
+  <si>
+    <t>Data\Input\MailsTemplates\Bot_FinalReport.html</t>
+  </si>
+  <si>
+    <t>Altfest_ClientEngagementTrackerUrl</t>
+  </si>
+  <si>
+    <t>Altfest_PractifiLoginUrl</t>
+  </si>
+  <si>
+    <t>Stores the direct access URL to the Practifi report used by Altfest.</t>
+  </si>
+  <si>
+    <t>Altfest_PractifiReportUrl</t>
+  </si>
+  <si>
+    <t>Stores the login URL used to access Practifi for Altfest.</t>
+  </si>
+  <si>
+    <t>MaxApiRetry</t>
+  </si>
+  <si>
+    <t>C:\Users\ALTFEST_DA_User2\L.J. Altfest &amp; Company\Altfest Document Library - Client Assignments\2026\2026 CLIENT ENGAGEMENT TRACKER.xlsx</t>
+  </si>
+  <si>
+    <t>Email address of the Altfest client team, used for notifications.</t>
+  </si>
+  <si>
+    <t>Support email address for the Altfest process.</t>
+  </si>
+  <si>
+    <t>URL of the Altfest client engagement tracker.</t>
+  </si>
+  <si>
+    <t>Data\Input\Prompt.txt</t>
+  </si>
+  <si>
+    <t>MatchesPromptFilePath</t>
+  </si>
+  <si>
+    <t>CellToWriteYes</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>Altfest_ApiKey</t>
+  </si>
+  <si>
+    <t>Altfest_CurrentFileDate</t>
+  </si>
+  <si>
+    <t>FullNamePositionMasterFile</t>
+  </si>
+  <si>
+    <t>MatchTablesPrompt</t>
+  </si>
+  <si>
+    <t>[DocumentFolderPath]\TaxReturnPt1\TaxReturnOutput_Template.xlsx</t>
+  </si>
+  <si>
+    <t>[DocumentFolderPath]\TaxReturnPt1\Output\[PreviousYear] Tax Returns Received [CurrentDate].xlsx</t>
+  </si>
+  <si>
+    <t>AssetCurrentFilePathName</t>
+  </si>
+  <si>
+    <t>TaxReturn1_LocalTrackerFilePath</t>
+  </si>
+  <si>
     <t>MasterFilePath</t>
-  </si>
-  <si>
-    <t>MasterFileSheet</t>
-  </si>
-  <si>
-    <t>MAIN SHEET</t>
-  </si>
-  <si>
-    <t>SubjectFinalEmail</t>
-  </si>
-  <si>
-    <t>[PreviousYear] Tax Returns Received</t>
-  </si>
-  <si>
-    <t>Altfest_CustomerMail</t>
-  </si>
-  <si>
-    <t>Altfest_SupportMail</t>
-  </si>
-  <si>
-    <t>BodyFinalEmail</t>
-  </si>
-  <si>
-    <t>Data\Input\MailsTemplates\Bot_FinalReport.html</t>
-  </si>
-  <si>
-    <t>Altfest_ClientEngagementTrackerUrl</t>
-  </si>
-  <si>
-    <t>Altfest_PractifiLoginUrl</t>
-  </si>
-  <si>
-    <t>Stores the direct access URL to the Practifi report used by Altfest.</t>
-  </si>
-  <si>
-    <t>Altfest_PractifiReportUrl</t>
-  </si>
-  <si>
-    <t>Stores the login URL used to access Practifi for Altfest.</t>
-  </si>
-  <si>
-    <t>MaxApiRetry</t>
-  </si>
-  <si>
-    <t>C:\Users\ALTFEST_DA_User2\L.J. Altfest &amp; Company\Altfest Document Library - Client Assignments\2026\2026 CLIENT ENGAGEMENT TRACKER.xlsx</t>
-  </si>
-  <si>
-    <t>Email address of the Altfest client team, used for notifications.</t>
-  </si>
-  <si>
-    <t>Support email address for the Altfest process.</t>
-  </si>
-  <si>
-    <t>URL of the Altfest client engagement tracker.</t>
-  </si>
-  <si>
-    <t>Data\Input\Prompt.txt</t>
-  </si>
-  <si>
-    <t>MatchesPromptFilePath</t>
-  </si>
-  <si>
-    <t>CellToWriteYes</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>Altfest_ApiKey</t>
-  </si>
-  <si>
-    <t>Altfest_CurrentFileDate</t>
-  </si>
-  <si>
-    <t>FullNamePositionMasterFile</t>
-  </si>
-  <si>
-    <t>MatchTablesPrompt</t>
-  </si>
-  <si>
-    <t>C:\Users\ALTFEST_DA_User1\Downloads\2026 CLIENT ENGAGEMENT TRACKER.xlsx</t>
-  </si>
-  <si>
-    <t>MasterFilePath1</t>
-  </si>
-  <si>
-    <t>[DocumentFolderPath]\TaxReturnPt1\TaxReturnOutput_Template.xlsx</t>
-  </si>
-  <si>
-    <t>[DocumentFolderPath]\TaxReturnPt1\Output\2025 Tax Returns Received 07.31.26.xlsx</t>
-  </si>
-  <si>
-    <t>[DocumentFolderPath]\TaxReturnPt1\Output\[PreviousYear] Tax Returns Received [CurrentDate].xlsx</t>
   </si>
 </sst>
 </file>
@@ -1771,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z986"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1967,7 +1964,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
@@ -1983,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
@@ -1994,94 +1991,87 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>81</v>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
         <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" t="s">
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>77</v>
-      </c>
     </row>
-    <row r="33" spans="1:2" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
@@ -3034,8 +3024,6 @@
     <row r="984" ht="14.25" customHeight="1"/>
     <row r="985" ht="14.25" customHeight="1"/>
     <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3092,87 +3080,107 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALTFEST_DA_User1\Documents\UiPath\Altfest_TaxReturnP1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C6E5F-8C2B-484A-AA81-EFC6572873FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79902AB-A00C-4C7B-A966-6E5768347F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
